--- a/docs/downloads/05/tbl_water_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_ambatoharanana.xlsx
@@ -405,12 +405,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Puits non aménagé (trou d?eau)</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -579,12 +567,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
